--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11423,7 +11423,7 @@
         <v>110266657</v>
       </c>
       <c r="B90" t="n">
-        <v>90029</v>
+        <v>90036</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11537,7 +11537,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Patrick Fritzson, Björn Bråvander</t>
+          <t>Björn Bråvander, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11551,7 +11551,7 @@
         <v>121268479</v>
       </c>
       <c r="B91" t="n">
-        <v>91620</v>
+        <v>91630</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>121268879</v>
       </c>
       <c r="B92" t="n">
-        <v>91620</v>
+        <v>91630</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11548,10 +11548,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121268479</v>
+        <v>121268879</v>
       </c>
       <c r="B91" t="n">
-        <v>91630</v>
+        <v>91642</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11599,10 +11599,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>644929</v>
+        <v>644948</v>
       </c>
       <c r="R91" t="n">
-        <v>6632335</v>
+        <v>6632371</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121268879</v>
+        <v>121268479</v>
       </c>
       <c r="B92" t="n">
-        <v>91630</v>
+        <v>91642</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11713,10 +11713,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>644948</v>
+        <v>644929</v>
       </c>
       <c r="R92" t="n">
-        <v>6632371</v>
+        <v>6632335</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11548,10 +11548,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121268879</v>
+        <v>121268479</v>
       </c>
       <c r="B91" t="n">
-        <v>91642</v>
+        <v>91643</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11599,10 +11599,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>644948</v>
+        <v>644929</v>
       </c>
       <c r="R91" t="n">
-        <v>6632371</v>
+        <v>6632335</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121268479</v>
+        <v>121268879</v>
       </c>
       <c r="B92" t="n">
-        <v>91642</v>
+        <v>91643</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11713,10 +11713,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>644929</v>
+        <v>644948</v>
       </c>
       <c r="R92" t="n">
-        <v>6632335</v>
+        <v>6632371</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11551,7 +11551,7 @@
         <v>121268479</v>
       </c>
       <c r="B91" t="n">
-        <v>91643</v>
+        <v>91646</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>121268879</v>
       </c>
       <c r="B92" t="n">
-        <v>91643</v>
+        <v>91646</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11551,7 +11551,7 @@
         <v>121268479</v>
       </c>
       <c r="B91" t="n">
-        <v>91646</v>
+        <v>91652</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>121268879</v>
       </c>
       <c r="B92" t="n">
-        <v>91646</v>
+        <v>91652</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11548,10 +11548,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121268479</v>
+        <v>121268879</v>
       </c>
       <c r="B91" t="n">
-        <v>91652</v>
+        <v>91653</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11599,10 +11599,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>644929</v>
+        <v>644948</v>
       </c>
       <c r="R91" t="n">
-        <v>6632335</v>
+        <v>6632371</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121268879</v>
+        <v>121268479</v>
       </c>
       <c r="B92" t="n">
-        <v>91652</v>
+        <v>91653</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11713,10 +11713,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>644948</v>
+        <v>644929</v>
       </c>
       <c r="R92" t="n">
-        <v>6632371</v>
+        <v>6632335</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11548,7 +11548,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121268879</v>
+        <v>121268479</v>
       </c>
       <c r="B91" t="n">
         <v>91653</v>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11599,10 +11599,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>644948</v>
+        <v>644929</v>
       </c>
       <c r="R91" t="n">
-        <v>6632371</v>
+        <v>6632335</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121268479</v>
+        <v>121268879</v>
       </c>
       <c r="B92" t="n">
         <v>91653</v>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11713,10 +11713,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>644929</v>
+        <v>644948</v>
       </c>
       <c r="R92" t="n">
-        <v>6632335</v>
+        <v>6632371</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11548,7 +11548,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121268479</v>
+        <v>121268879</v>
       </c>
       <c r="B91" t="n">
         <v>91653</v>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11599,10 +11599,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>644929</v>
+        <v>644948</v>
       </c>
       <c r="R91" t="n">
-        <v>6632335</v>
+        <v>6632371</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121268879</v>
+        <v>121268479</v>
       </c>
       <c r="B92" t="n">
         <v>91653</v>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11713,10 +11713,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>644948</v>
+        <v>644929</v>
       </c>
       <c r="R92" t="n">
-        <v>6632371</v>
+        <v>6632335</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,111 @@
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>125712614</v>
+      </c>
+      <c r="B93" t="n">
+        <v>90730</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Nåsten, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>644863</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6632322</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Uppsala-Näs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11779,7 +11779,7 @@
         <v>125712614</v>
       </c>
       <c r="B93" t="n">
-        <v>90730</v>
+        <v>90737</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11779,7 +11779,7 @@
         <v>125712614</v>
       </c>
       <c r="B93" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11779,7 +11779,7 @@
         <v>125712614</v>
       </c>
       <c r="B93" t="n">
-        <v>90738</v>
+        <v>90742</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11779,7 +11779,7 @@
         <v>125712614</v>
       </c>
       <c r="B93" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11779,7 +11779,7 @@
         <v>125712614</v>
       </c>
       <c r="B93" t="n">
-        <v>90744</v>
+        <v>90746</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11779,7 +11779,7 @@
         <v>125712614</v>
       </c>
       <c r="B93" t="n">
-        <v>90746</v>
+        <v>90748</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 56218-2019 artfynd.xlsx
+++ b/artfynd/A 56218-2019 artfynd.xlsx
@@ -11779,7 +11779,7 @@
         <v>125712614</v>
       </c>
       <c r="B93" t="n">
-        <v>90748</v>
+        <v>90752</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
